--- a/kantei_db.xlsx
+++ b/kantei_db.xlsx
@@ -44943,7 +44943,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>セレブ</t>
+          <t>セレブMIX</t>
         </is>
       </c>
     </row>
@@ -44965,7 +44965,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>セレブ</t>
+          <t>セレブMIX</t>
         </is>
       </c>
     </row>
@@ -45031,7 +45031,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ラバー</t>
+          <t>ラバーMIX</t>
         </is>
       </c>
     </row>
@@ -45053,7 +45053,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ラバー</t>
+          <t>ラバーMIX</t>
         </is>
       </c>
     </row>
@@ -45075,7 +45075,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>エキスパート</t>
+          <t>エキスパートMIX</t>
         </is>
       </c>
     </row>
@@ -45097,7 +45097,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>エキスパート</t>
+          <t>エキスパートMIX</t>
         </is>
       </c>
     </row>
@@ -45163,7 +45163,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>キング</t>
+          <t>キングMIX</t>
         </is>
       </c>
     </row>
@@ -45185,7 +45185,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>キング</t>
+          <t>キングMIX</t>
         </is>
       </c>
     </row>
